--- a/inventories/lci-open-prom.xlsx
+++ b/inventories/lci-open-prom.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\terlouw_t\Documents\Projects\TRANSIENCE\lca_transience\inventories\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\terlouw_t\Documents\Projects\TRANSIENCE\lca_port_of_rotterdam\inventories\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEBDF782-C22A-4D70-BCF3-9CED4ED68485}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9FEC5DB-D7DF-4248-AA15-51A4A084F598}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28740" yWindow="-21600" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="lci" sheetId="9" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10052" uniqueCount="612">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10052" uniqueCount="615">
   <si>
     <t>Activity</t>
   </si>
@@ -1837,12 +1837,6 @@
     <t>electricity for industrial applications</t>
   </si>
   <si>
-    <t>carbon dioxide, captured from atmosphere and stored, with a sorbent-based direct air capture system, 100ktCO2</t>
-  </si>
-  <si>
-    <t>carbon dioxide, captured from atmosphere</t>
-  </si>
-  <si>
     <t>carbon dioxide removal, with direct air capture</t>
   </si>
   <si>
@@ -1852,9 +1846,6 @@
     <t>carbon dioxide removal, with a wood burning power plant with carbon capture and storage</t>
   </si>
   <si>
-    <t>carbon dioxide, captured from atmosphere and stored, with a solvent-based direct air capture system, 1MtCO2</t>
-  </si>
-  <si>
     <t>hydrogen burned, in hydrogen boiler, residential</t>
   </si>
   <si>
@@ -1880,6 +1871,24 @@
   </si>
   <si>
     <t>36 MJ/m³</t>
+  </si>
+  <si>
+    <t>carbon dioxide, captured and stored, with a sorbent-based direct air capture system, 100ktCO2</t>
+  </si>
+  <si>
+    <t>carbon dioxide, captured and stored, with a solvent-based direct air capture system, 1MtCO2</t>
+  </si>
+  <si>
+    <t>carbon dioxide, captured</t>
+  </si>
+  <si>
+    <t>natural gas, burned in residential natural gas boiler</t>
+  </si>
+  <si>
+    <t>hard coal, burned in hard coal industrial furnace</t>
+  </si>
+  <si>
+    <t>light fuel oil, burned in industrial furnace</t>
   </si>
 </sst>
 </file>
@@ -2264,7 +2273,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -2563,7 +2572,7 @@
         <v>116</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15.6">
@@ -2748,7 +2757,7 @@
         <v>0</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>292</v>
+        <v>614</v>
       </c>
       <c r="C14" s="53"/>
       <c r="D14" s="53"/>
@@ -2868,7 +2877,7 @@
     <row r="22" spans="1:8">
       <c r="A22" s="53" t="str">
         <f>B14</f>
-        <v>light fuel oil, burned in industrial furnace 1MW</v>
+        <v>light fuel oil, burned in industrial furnace</v>
       </c>
       <c r="B22" s="53">
         <v>1</v>
@@ -3087,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>299</v>
+        <v>613</v>
       </c>
       <c r="C36" s="53"/>
       <c r="D36" s="53"/>
@@ -3200,7 +3209,7 @@
     <row r="44" spans="1:8">
       <c r="A44" s="53" t="str">
         <f>B36</f>
-        <v>hard coal, burned in hard coal industrial furnace 1-10MW</v>
+        <v>hard coal, burned in hard coal industrial furnace</v>
       </c>
       <c r="B44" s="53">
         <v>1</v>
@@ -3883,7 +3892,7 @@
         <v>0</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>348</v>
+        <v>612</v>
       </c>
       <c r="C86" s="53"/>
       <c r="D86" s="53"/>
@@ -3996,7 +4005,7 @@
     <row r="94" spans="1:8">
       <c r="A94" s="53" t="str">
         <f>B86</f>
-        <v>natural gas, burned in residential natural gas boiler &lt;100kW</v>
+        <v>natural gas, burned in residential natural gas boiler</v>
       </c>
       <c r="B94" s="53">
         <v>1</v>
@@ -7163,7 +7172,7 @@
         <v>0</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C285" s="53"/>
       <c r="D285" s="53"/>
@@ -7483,7 +7492,7 @@
         <v>0</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="C307" s="53"/>
       <c r="D307" s="53"/>
@@ -7617,12 +7626,12 @@
         <v>carbon dioxide removal, with direct air capture</v>
       </c>
       <c r="H315" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
     </row>
     <row r="316" spans="1:8">
       <c r="A316" t="s">
-        <v>597</v>
+        <v>609</v>
       </c>
       <c r="B316">
         <v>0.5</v>
@@ -7637,12 +7646,12 @@
         <v>18</v>
       </c>
       <c r="G316" t="s">
-        <v>598</v>
+        <v>611</v>
       </c>
     </row>
     <row r="317" spans="1:8">
       <c r="A317" t="s">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="B317">
         <v>0.5</v>
@@ -7657,7 +7666,7 @@
         <v>18</v>
       </c>
       <c r="G317" t="s">
-        <v>598</v>
+        <v>611</v>
       </c>
     </row>
     <row r="319" spans="1:8" ht="15.6">
@@ -7665,7 +7674,7 @@
         <v>0</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="C319" s="53"/>
       <c r="D319" s="53"/>
@@ -7945,7 +7954,7 @@
         <v>0</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="C336" s="53"/>
       <c r="D336" s="53"/>
@@ -7984,7 +7993,7 @@
         <v>3</v>
       </c>
       <c r="B339" s="53" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="C339" s="53"/>
       <c r="D339" s="53"/>
@@ -8082,7 +8091,7 @@
     </row>
     <row r="345" spans="1:8">
       <c r="A345" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="B345" s="3">
         <f>1/45</f>
@@ -8098,10 +8107,10 @@
         <v>18</v>
       </c>
       <c r="G345" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="H345" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
     </row>
     <row r="346" spans="1:8">
@@ -8112,7 +8121,7 @@
         <v>0</v>
       </c>
       <c r="B347" s="1" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="C347" s="53"/>
       <c r="D347" s="53"/>
@@ -8151,7 +8160,7 @@
         <v>3</v>
       </c>
       <c r="B350" s="53" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="C350" s="53"/>
       <c r="D350" s="53"/>
@@ -8265,7 +8274,7 @@
         <v>18</v>
       </c>
       <c r="G356" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="H356" t="s">
         <v>383</v>

--- a/inventories/lci-open-prom.xlsx
+++ b/inventories/lci-open-prom.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\terlouw_t\Documents\Projects\TRANSIENCE\lca_port_of_rotterdam\inventories\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\terlouw_t\Documents\Projects\TRANSIENCE\lca_transience\inventories\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9FEC5DB-D7DF-4248-AA15-51A4A084F598}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79DD8816-9578-48AC-A195-17850C86110D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28740" yWindow="-21600" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33885" yWindow="-21600" windowWidth="20865" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="lci" sheetId="9" r:id="rId1"/>

--- a/inventories/lci-open-prom.xlsx
+++ b/inventories/lci-open-prom.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\terlouw_t\Documents\Projects\TRANSIENCE\lca_transience\inventories\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79DD8816-9578-48AC-A195-17850C86110D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60E4FBED-73FA-4634-9D01-270552DE9440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33885" yWindow="-21600" windowWidth="20865" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28740" yWindow="-21600" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="lci" sheetId="9" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10052" uniqueCount="615">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10052" uniqueCount="618">
   <si>
     <t>Activity</t>
   </si>
@@ -1889,6 +1889,15 @@
   </si>
   <si>
     <t>light fuel oil, burned in industrial furnace</t>
+  </si>
+  <si>
+    <t>fuel tank, compressed hydrogen gas, 700bar, with HDPE liner, carculator passenger car 2020</t>
+  </si>
+  <si>
+    <t>hydrogen tank</t>
+  </si>
+  <si>
+    <t>electricity production, photovoltaic, 3kWp slanted-roof installation, multi-Si, laminated, integrated</t>
   </si>
 </sst>
 </file>
@@ -4504,7 +4513,7 @@
     </row>
     <row r="129" spans="1:11">
       <c r="A129" t="s">
-        <v>503</v>
+        <v>617</v>
       </c>
       <c r="B129" s="3">
         <v>1</v>
@@ -5065,7 +5074,7 @@
     </row>
     <row r="170" spans="1:11">
       <c r="A170" t="s">
-        <v>399</v>
+        <v>615</v>
       </c>
       <c r="B170">
         <f>802/1000000/10.95</f>
@@ -5081,7 +5090,7 @@
         <v>18</v>
       </c>
       <c r="G170" t="s">
-        <v>398</v>
+        <v>616</v>
       </c>
       <c r="H170">
         <v>5</v>
